--- a/ig/nr-deploy-1.0.0-ballot/CodeSystem-type-systeme-information-cs.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/CodeSystem-type-systeme-information-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/CodeSystem/type-systeme-information-cs</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/CodeSystem/type-systeme-information-cs</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T12:29:31+00:00</t>
+    <t>2023-06-02T14:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-deploy-1.0.0-ballot/CodeSystem-type-systeme-information-cs.xlsx
+++ b/ig/nr-deploy-1.0.0-ballot/CodeSystem-type-systeme-information-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-02T14:39:58+00:00</t>
+    <t>2023-06-02T15:19:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>CG</t>
+  </si>
+  <si>
+    <t>SI CPS</t>
   </si>
 </sst>
 </file>
@@ -521,7 +524,7 @@
         <v>46</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
